--- a/reports/pdf_weekly_20261008.xlsx
+++ b/reports/pdf_weekly_20261008.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,416억   ·   현금 1억(0.0%)      주말 2026-10-08  vs  주초 2026-10-06      매수 6종목  /  매도 20종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,326억   ·   현금 1억(0.0%)      주말 2026-10-08  vs  주초 2026-10-06      매수 6종목  /  매도 20종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>230</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3494713507</v>
+        <v>3519827067</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-219</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2418891083</v>
+        <v>-2436273614</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>83</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>6887741370</v>
+        <v>6937237761</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-46</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1462851231</v>
+        <v>-1473363510</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>29</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1587425885</v>
+        <v>1598833376</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-31</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-475555705</v>
+        <v>-478973123</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>28</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>552258238</v>
+        <v>556226853</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-28</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-322355179</v>
+        <v>-324671674</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>27</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1044031050</v>
+        <v>1051533621</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-15</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-956955413</v>
+        <v>-963832245</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>502584217</v>
+        <v>506195866</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-14</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-490214411</v>
+        <v>-493737169</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>-13</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-85975017</v>
+        <v>-86592847</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -960,14 +960,14 @@
       <c r="E13" s="17" t="n"/>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스 ※</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-278758920</v>
+        <v>-280762126</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>-11</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1014616238</v>
+        <v>-1021907429</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>-11</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1032830045</v>
+        <v>-1040252124</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>-9</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-705663304</v>
+        <v>-710734312</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1072,23 +1072,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-192949483</v>
+        <v>-494423869</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.39%</t>
+          <t>0.41%→0.33%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>81→74</t>
+          <t>32→25</t>
         </is>
       </c>
     </row>
@@ -1100,23 +1100,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-490896212</v>
+        <v>-194336048</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.33%</t>
+          <t>0.42%→0.39%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>32→25</t>
+          <t>81→74</t>
         </is>
       </c>
     </row>
@@ -1128,23 +1128,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-140548261</v>
+        <v>-540923257</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.40%</t>
+          <t>0.51%→0.42%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1156,23 +1156,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-537063832</v>
+        <v>-141558262</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.42%</t>
+          <t>0.42%→0.40%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1184,23 +1184,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-246909106</v>
+        <v>-253588433</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.06%</t>
+          <t>1.55%→1.45%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>11→6</t>
+          <t>157→152</t>
         </is>
       </c>
     </row>
@@ -1212,23 +1212,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-251779109</v>
+        <v>-248683434</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>1.55%→1.45%</t>
+          <t>0.10%→0.06%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>157→152</t>
+          <t>11→6</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
         <v>-4</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-113958049</v>
+        <v>-114776970</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>-4</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-794784343</v>
+        <v>-800495788</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>-3</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-901437389</v>
+        <v>-907915259</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,499억   ·   현금 55억(1.6%)      주말 2026-10-08  vs  주초 2026-10-06      매수 6종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,467억   ·   현금 27억(0.8%)      주말 2026-10-08  vs  주초 2026-10-06      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1415,7 +1415,7 @@
         <v>72</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1018756994</v>
+        <v>1020693871</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>-176</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1664516796</v>
+        <v>-1667681403</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>63</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1481268882</v>
+        <v>1484085094</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>-122</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1010709192</v>
+        <v>-1012630769</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>354997467</v>
+        <v>355672394</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>-16</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-1032643396</v>
+        <v>-1034606675</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>13</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>313180460</v>
+        <v>313775883</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>-10</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-686430130</v>
+        <v>-687735183</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>12</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>322543261</v>
+        <v>323156486</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>4</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>308867259</v>
+        <v>309454482</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,947억   ·   현금 83억(2.9%)      주말 2026-10-08  vs  주초 2026-10-06      매수 1종목  /  매도 2종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,834억   ·   현금 41억(1.5%)      주말 2026-10-08  vs  주초 2026-10-06      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1736,7 +1736,7 @@
         <v>10</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2095081138</v>
+        <v>2101400695</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>-197</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-1290437381</v>
+        <v>-1294329828</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>-26</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1251479480</v>
+        <v>-1255254415</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,198억   ·   현금 15억(0.7%)      주말 2026-10-08  vs  주초 2026-10-06      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,225억   ·   현금 8억(0.4%)      주말 2026-10-08  vs  주초 2026-10-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -1825,7 +1825,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 325억   ·   현금 5억(1.7%)      주말 2026-10-08  vs  주초 2026-10-06      매수 2종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 315억   ·   현금 3억(0.9%)      주말 2026-10-08  vs  주초 2026-10-06      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -1921,7 +1921,7 @@
         <v>89</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>95500560</v>
+        <v>94411172</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -1942,11 +1942,11 @@
         <v>-78</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-64072320</v>
+        <v>-63011501</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>1.70%→1.51%</t>
+          <t>1.73%→1.53%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -1965,11 +1965,11 @@
         <v>16</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>39984000</v>
+        <v>40854388</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>1.10%→1.23%</t>
+          <t>1.16%→1.29%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -1986,11 +1986,11 @@
         <v>-60</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-61281600</v>
+        <v>-58343983</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.70%→0.51%</t>
+          <t>0.68%→0.50%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2014,11 +2014,11 @@
         <v>-17</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-31269800</v>
+        <v>-30055991</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>4.95%→4.86%</t>
+          <t>4.91%→4.82%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2042,11 +2042,11 @@
         <v>-10</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-63920000</v>
+        <v>-64395981</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.19%→0.99%</t>
+          <t>1.24%→1.03%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,223억      주말 2026-10-08  vs  주초 2026-10-06      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,210억      주말 2026-10-08  vs  주초 2026-10-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>

--- a/reports/pdf_weekly_20261008.xlsx
+++ b/reports/pdf_weekly_20261008.xlsx
@@ -988,23 +988,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1021907429</v>
+        <v>-1040252124</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.84%</t>
+          <t>0.72%→0.55%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>42→31</t>
         </is>
       </c>
     </row>
@@ -1016,23 +1016,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1040252124</v>
+        <v>-1021907429</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.55%</t>
+          <t>1.03%→0.84%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>42→31</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -1072,23 +1072,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-494423869</v>
+        <v>-194336048</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.33%</t>
+          <t>0.42%→0.39%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>32→25</t>
+          <t>81→74</t>
         </is>
       </c>
     </row>
@@ -1100,23 +1100,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-194336048</v>
+        <v>-494423869</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.39%</t>
+          <t>0.41%→0.33%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>81→74</t>
+          <t>32→25</t>
         </is>
       </c>
     </row>
@@ -1128,23 +1128,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-540923257</v>
+        <v>-141558262</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.42%</t>
+          <t>0.42%→0.40%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1156,23 +1156,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-141558262</v>
+        <v>-540923257</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.40%</t>
+          <t>0.51%→0.42%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1184,23 +1184,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-253588433</v>
+        <v>-248683434</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.55%→1.45%</t>
+          <t>0.10%→0.06%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>157→152</t>
+          <t>11→6</t>
         </is>
       </c>
     </row>
@@ -1212,23 +1212,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-248683434</v>
+        <v>-253588433</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.06%</t>
+          <t>1.55%→1.45%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>11→6</t>
+          <t>157→152</t>
         </is>
       </c>
     </row>
@@ -1240,23 +1240,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-114776970</v>
+        <v>-800495788</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.02%→0.00%</t>
+          <t>6.79%→6.99%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>4→0</t>
+          <t>190→186</t>
         </is>
       </c>
     </row>
@@ -1268,23 +1268,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-800495788</v>
+        <v>-114776970</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>6.79%→6.99%</t>
+          <t>0.02%→0.00%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>190→186</t>
+          <t>4→0</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20261008.xlsx
+++ b/reports/pdf_weekly_20261008.xlsx
@@ -1072,23 +1072,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-194336048</v>
+        <v>-494423869</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.39%</t>
+          <t>0.41%→0.33%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>81→74</t>
+          <t>32→25</t>
         </is>
       </c>
     </row>
@@ -1100,23 +1100,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-494423869</v>
+        <v>-194336048</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.33%</t>
+          <t>0.42%→0.39%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>32→25</t>
+          <t>81→74</t>
         </is>
       </c>
     </row>
@@ -1128,23 +1128,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-141558262</v>
+        <v>-540923257</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.40%</t>
+          <t>0.51%→0.42%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1156,23 +1156,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-540923257</v>
+        <v>-141558262</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.42%</t>
+          <t>0.42%→0.40%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20261008.xlsx
+++ b/reports/pdf_weekly_20261008.xlsx
@@ -988,23 +988,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1040252124</v>
+        <v>-1021907429</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.55%</t>
+          <t>1.03%→0.84%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>42→31</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -1016,23 +1016,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1021907429</v>
+        <v>-1040252124</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.84%</t>
+          <t>0.72%→0.55%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>42→31</t>
         </is>
       </c>
     </row>
@@ -1072,23 +1072,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-494423869</v>
+        <v>-194336048</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.33%</t>
+          <t>0.42%→0.39%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>32→25</t>
+          <t>81→74</t>
         </is>
       </c>
     </row>
@@ -1100,23 +1100,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-194336048</v>
+        <v>-494423869</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.39%</t>
+          <t>0.41%→0.33%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>81→74</t>
+          <t>32→25</t>
         </is>
       </c>
     </row>
@@ -1184,23 +1184,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-248683434</v>
+        <v>-253588433</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.06%</t>
+          <t>1.55%→1.45%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>11→6</t>
+          <t>157→152</t>
         </is>
       </c>
     </row>
@@ -1212,23 +1212,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-253588433</v>
+        <v>-248683434</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>1.55%→1.45%</t>
+          <t>0.10%→0.06%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>157→152</t>
+          <t>11→6</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20261008.xlsx
+++ b/reports/pdf_weekly_20261008.xlsx
@@ -988,23 +988,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1021907429</v>
+        <v>-1040252124</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.84%</t>
+          <t>0.72%→0.55%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>42→31</t>
         </is>
       </c>
     </row>
@@ -1016,23 +1016,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1040252124</v>
+        <v>-1021907429</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.55%</t>
+          <t>1.03%→0.84%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>42→31</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -1072,23 +1072,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-194336048</v>
+        <v>-494423869</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.39%</t>
+          <t>0.41%→0.33%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>81→74</t>
+          <t>32→25</t>
         </is>
       </c>
     </row>
@@ -1100,23 +1100,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-494423869</v>
+        <v>-194336048</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.33%</t>
+          <t>0.42%→0.39%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>32→25</t>
+          <t>81→74</t>
         </is>
       </c>
     </row>
@@ -1128,23 +1128,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-540923257</v>
+        <v>-141558262</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.42%</t>
+          <t>0.42%→0.40%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1156,23 +1156,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-141558262</v>
+        <v>-540923257</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.40%</t>
+          <t>0.51%→0.42%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1240,23 +1240,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-800495788</v>
+        <v>-114776970</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>6.79%→6.99%</t>
+          <t>0.02%→0.00%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>190→186</t>
+          <t>4→0</t>
         </is>
       </c>
     </row>
@@ -1268,23 +1268,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-114776970</v>
+        <v>-800495788</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.02%→0.00%</t>
+          <t>6.79%→6.99%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>4→0</t>
+          <t>190→186</t>
         </is>
       </c>
     </row>
